--- a/_work/analysis/02_сравнение_гарантия.xlsx
+++ b/_work/analysis/02_сравнение_гарантия.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Остатки чужих данных" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Статус и полнота чтения" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Проверка цитат" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Поправки (этап 3)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -70,6 +76,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6961,4 +6968,119 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>При подготовке этапа 3 найдены неточности этапа 2. Лист «Сравнение» не переписан: читайте его вместе с этим листом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Было в таблице этапа 2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Исправление (по исходному тексту)</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Как проверено</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Применимое право; пропорциональное уменьшение (п. 2.3); безакцептное списание суммы неустойки</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>отмечены как условия части договоров / только №46</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>есть во всех 12 договорах (в №51 — «право на списание (изъятие)», без слова «безакцептное»)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>поиск по текстовым копиям всех 12 договоров, этап 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Основные термины</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>в №24 ЗКО Прил.4 определения «Гарантия» нет</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>есть: раздел «Основные термины и определения», «Гарантия — способ обеспечения исполнения обязательств Заемщика…» (текстовая копия, стр. 2522–2523)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>чтение текстовой копии, этап 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Сохранение действия договора / предъявление требований</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>№51 Жетісу, п. 5.5</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>№51 Жетісу, п. 2.4 («требования … могут предъявляться … один и более раз…»)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>чтение текстовой копии, этап 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/_work/analysis/02_сравнение_гарантия.xlsx
+++ b/_work/analysis/02_сравнение_гарантия.xlsx
@@ -6976,7 +6976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7080,6 +7080,28 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Термины / основное обязательство</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>№20 Жамбыл: в п. 1.1 определён «Кредитный договор», далее по тексту — «Договор о предоставлении кредита» (новый внутренний дефект, выявлен на этапе 4)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>агент этапа 4 по тексту</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
